--- a/src/nodes/P/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/P/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>35.938888349939567</v>
+        <v>39.862556628958359</v>
       </c>
       <c r="B1">
-        <v>40.168695079421653</v>
+        <v>44.397566988426867</v>
       </c>
       <c r="C1">
         <v>338.08353538342624</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>33.083049979843835</v>
+        <v>37.357414832338371</v>
       </c>
       <c r="B2">
-        <v>38.814547633821995</v>
+        <v>42.691705484727251</v>
       </c>
       <c r="C2">
         <v>338.08353538342624</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>30.531929795020826</v>
+        <v>34.878701378210231</v>
       </c>
       <c r="B3">
-        <v>37.154638631796061</v>
+        <v>40.9593128820354</v>
       </c>
       <c r="C3">
         <v>338.08353538342624</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>28.03569325175874</v>
+        <v>32.421434673639283</v>
       </c>
       <c r="B4">
-        <v>35.439658063723009</v>
+        <v>39.205390142304552</v>
       </c>
       <c r="C4">
         <v>338.08353538342624</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>25.580427566807241</v>
+        <v>29.980633125690865</v>
       </c>
       <c r="B5">
-        <v>33.68356635095752</v>
+        <v>37.434938227487891</v>
       </c>
       <c r="C5">
         <v>338.08353538342624</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>23.160445845665812</v>
+        <v>27.55342469954007</v>
       </c>
       <c r="B6">
-        <v>31.8920698602271</v>
+        <v>35.650840339219158</v>
       </c>
       <c r="C6">
         <v>338.08353538342624</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>20.772493169567618</v>
+        <v>25.145375592800992</v>
       </c>
       <c r="B7">
-        <v>30.068434655312288</v>
+        <v>33.847508637854013</v>
       </c>
       <c r="C7">
         <v>338.08353538342624</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>18.414647117240683</v>
+        <v>22.762349434779217</v>
       </c>
       <c r="B8">
-        <v>28.214589739956995</v>
+        <v>32.019056695607276</v>
       </c>
       <c r="C8">
         <v>338.08353538342624</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>16.083917251030261</v>
+        <v>20.40296134910734</v>
       </c>
       <c r="B9">
-        <v>26.333535791232364</v>
+        <v>30.166874773408367</v>
       </c>
       <c r="C9">
         <v>338.08353538342624</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>13.777077625890286</v>
+        <v>18.064526782117454</v>
       </c>
       <c r="B10">
-        <v>24.428509799990621</v>
+        <v>28.293657862785235</v>
       </c>
       <c r="C10">
         <v>338.08353538342624</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>11.491028283592057</v>
+        <v>15.746410976612539</v>
       </c>
       <c r="B11">
-        <v>22.502622338881078</v>
+        <v>26.400043188945435</v>
       </c>
       <c r="C11">
         <v>338.08353538342624</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>9.2241074577926678</v>
+        <v>13.448491624513327</v>
       </c>
       <c r="B12">
-        <v>20.557540864222339</v>
+        <v>24.48615353551644</v>
       </c>
       <c r="C12">
         <v>338.08353538342624</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>6.9802801628749487</v>
+        <v>11.170646417740532</v>
       </c>
       <c r="B13">
-        <v>18.589286785212998</v>
+        <v>22.552111686125706</v>
       </c>
       <c r="C13">
         <v>338.08353538342624</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>4.7619132108979842</v>
+        <v>8.9127474888297229</v>
       </c>
       <c r="B14">
-        <v>16.59548518570454</v>
+        <v>20.598046005401383</v>
       </c>
       <c r="C14">
         <v>338.08353538342624</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>2.5593538239001186</v>
+        <v>6.6746447327758567</v>
       </c>
       <c r="B15">
-        <v>14.585821895279953</v>
+        <v>18.624107181974416</v>
       </c>
       <c r="C15">
         <v>338.08353538342624</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>0.36374853646359112</v>
+        <v>4.4561824851887426</v>
       </c>
       <c r="B16">
-        <v>12.569180694089999</v>
+        <v>16.630451485476428</v>
       </c>
       <c r="C16">
         <v>338.08353538342624</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.8185392766330732</v>
+        <v>2.2572050816781797</v>
       </c>
       <c r="B17">
-        <v>10.539176418824965</v>
+        <v>14.617235185539055</v>
       </c>
       <c r="C17">
         <v>338.08353538342624</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.9792886305946782</v>
+        <v>0.077616432079838024</v>
       </c>
       <c r="B18">
-        <v>8.4875599356036915</v>
+        <v>12.584554745936467</v>
       </c>
       <c r="C18">
         <v>338.08353538342624</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-6.1180649407555778</v>
+        <v>-2.0824412568671455</v>
       </c>
       <c r="B19">
-        <v>6.4138951717197239</v>
+        <v>10.532267407013048</v>
       </c>
       <c r="C19">
         <v>338.08353538342624</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-8.2363802224825537</v>
+        <v>-4.2227662041978018</v>
       </c>
       <c r="B20">
-        <v>4.3196993197602422</v>
+        <v>8.460170603255694</v>
       </c>
       <c r="C20">
         <v>338.08353538342624</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-10.335746491142341</v>
+        <v>-6.343156628947126</v>
       </c>
       <c r="B21">
-        <v>2.2064895723124671</v>
+        <v>6.368061769151339</v>
       </c>
       <c r="C21">
         <v>338.08353538342624</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-12.417406098943582</v>
+        <v>-8.443478010471809</v>
       </c>
       <c r="B22">
-        <v>0.0755125354645475</v>
+        <v>4.2558058610245739</v>
       </c>
       <c r="C22">
         <v>338.08353538342624</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-14.481522745462311</v>
+        <v>-10.523864869415162</v>
       </c>
       <c r="B23">
-        <v>-2.0730675306914619</v>
+        <v>2.1235379225508013</v>
       </c>
       <c r="C23">
         <v>338.08353538342624</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-16.527990467116442</v>
+        <v>-12.584518986742181</v>
       </c>
       <c r="B24">
-        <v>-4.2393569525625541</v>
+        <v>-0.0285394807568954</v>
       </c>
       <c r="C24">
         <v>338.08353538342624</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-18.556703300323885</v>
+        <v>-14.625642143417847</v>
       </c>
       <c r="B25">
-        <v>-6.4234620565557208</v>
+        <v>-2.200223783385435</v>
       </c>
       <c r="C25">
         <v>338.08353538342624</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-20.5675099133087</v>
+        <v>-16.647376546181292</v>
       </c>
       <c r="B26">
-        <v>-8.6255346926148864</v>
+        <v>-4.3913722256791807</v>
       </c>
       <c r="C26">
         <v>338.08353538342624</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-22.560077501519576</v>
+        <v>-18.649626104868187</v>
       </c>
       <c r="B27">
-        <v>-10.845908804831726</v>
+        <v>-6.6020812714123158</v>
       </c>
       <c r="C27">
         <v>338.08353538342624</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-24.534027892211345</v>
+        <v>-20.632235155088324</v>
       </c>
       <c r="B28">
-        <v>-13.084963860834844</v>
+        <v>-8.832507190216468</v>
       </c>
       <c r="C28">
         <v>338.08353538342624</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-26.488982912638846</v>
+        <v>-22.595048032451519</v>
       </c>
       <c r="B29">
-        <v>-15.34307932825285</v>
+        <v>-11.08280625172327</v>
       </c>
       <c r="C29">
         <v>338.08353538342624</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-28.424763275247845</v>
+        <v>-24.537914631952734</v>
       </c>
       <c r="B30">
-        <v>-17.620435108530021</v>
+        <v>-13.353129144563651</v>
       </c>
       <c r="C30">
         <v>338.08353538342624</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-30.341985233247794</v>
+        <v>-26.460707086127528</v>
       </c>
       <c r="B31">
-        <v>-19.9164128383734</v>
+        <v>-15.643604233365776</v>
       </c>
       <c r="C31">
         <v>338.08353538342624</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-32.241463925039071</v>
+        <v>-28.363303086896622</v>
       </c>
       <c r="B32">
-        <v>-22.230194588305668</v>
+        <v>-17.9543543017571</v>
       </c>
       <c r="C32">
         <v>338.08353538342624</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-34.124014489022045</v>
+        <v>-30.24558032618074</v>
       </c>
       <c r="B33">
-        <v>-24.560962428849557</v>
+        <v>-20.285502133365092</v>
       </c>
       <c r="C33">
         <v>338.08353538342624</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-35.990127622267558</v>
+        <v>-32.106904046782873</v>
       </c>
       <c r="B34">
-        <v>-26.908223982761534</v>
+        <v>-22.637684953397304</v>
       </c>
       <c r="C34">
         <v>338.08353538342624</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-37.838996256528318</v>
+        <v>-33.944589695035113</v>
       </c>
       <c r="B35">
-        <v>-29.272789081733215</v>
+        <v>-25.013597753381703</v>
       </c>
       <c r="C35">
         <v>338.08353538342624</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-39.669488882227405</v>
+        <v>-35.757252394570031</v>
       </c>
       <c r="B36">
-        <v>-31.655793109689974</v>
+        <v>-27.414630794247667</v>
       </c>
       <c r="C36">
         <v>338.08353538342624</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-41.480473989788</v>
+        <v>-37.550755774693243</v>
       </c>
       <c r="B37">
-        <v>-34.058371450557217</v>
+        <v>-29.834897648210049</v>
       </c>
       <c r="C37">
         <v>338.08353538342624</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-43.270026268132462</v>
+        <v>-39.330666033018829</v>
       </c>
       <c r="B38">
-        <v>-36.482456007779362</v>
+        <v>-32.268810475624512</v>
       </c>
       <c r="C38">
         <v>338.08353538342624</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-45.033045200180041</v>
+        <v>-41.0941111347219</v>
       </c>
       <c r="B39">
-        <v>-38.93316476287692</v>
+        <v>-34.719252478124794</v>
       </c>
       <c r="C39">
         <v>338.08353538342624</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-46.763636467349166</v>
+        <v>-42.836109486867755</v>
       </c>
       <c r="B40">
-        <v>-41.416412216889412</v>
+        <v>-37.191224617664069</v>
       </c>
       <c r="C40">
         <v>338.08353538342624</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-48.45590575105831</v>
+        <v>-44.551679496521771</v>
       </c>
       <c r="B41">
-        <v>-43.9381128708564</v>
+        <v>-39.689727856195553</v>
       </c>
       <c r="C41">
         <v>338.08353538342624</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-48.45590575105831</v>
+        <v>-44.324643800441294</v>
       </c>
       <c r="B42">
-        <v>-43.9381128708564</v>
+        <v>-39.91764629373435</v>
       </c>
       <c r="C42">
         <v>338.08353538342624</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-46.486785609592232</v>
+        <v>-42.377722187711413</v>
       </c>
       <c r="B43">
-        <v>-41.694211026599248</v>
+        <v>-37.651394180490477</v>
       </c>
       <c r="C43">
         <v>338.08353538342624</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-44.526890429935264</v>
+        <v>-40.428139759552487</v>
       </c>
       <c r="B44">
-        <v>-39.441052633776721</v>
+        <v>-35.3878132282386</v>
       </c>
       <c r="C44">
         <v>338.08353538342624</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-42.570397085586663</v>
+        <v>-38.470984985485721</v>
       </c>
       <c r="B45">
-        <v>-37.184480757582115</v>
+        <v>-33.131834064065011</v>
       </c>
       <c r="C45">
         <v>338.08353538342624</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-40.611482450045735</v>
+        <v>-36.501346335032359</v>
       </c>
       <c r="B46">
-        <v>-34.930338463208727</v>
+        <v>-30.888387315056043</v>
       </c>
       <c r="C46">
         <v>338.08353538342624</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-38.6451146406731</v>
+        <v>-34.516419950615266</v>
       </c>
       <c r="B47">
-        <v>-32.683674862727734</v>
+        <v>-28.660287740516431</v>
       </c>
       <c r="C47">
         <v>338.08353538342624</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-36.669426750274951</v>
+        <v>-32.5218326662641</v>
       </c>
       <c r="B48">
-        <v>-30.446363255721732</v>
+        <v>-26.441886628624825</v>
       </c>
       <c r="C48">
         <v>338.08353538342624</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-34.683343115518817</v>
+        <v>-30.523505940220684</v>
       </c>
       <c r="B49">
-        <v>-28.219482988651198</v>
+        <v>-24.227239497814026</v>
       </c>
       <c r="C49">
         <v>338.08353538342624</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-32.685788073072288</v>
+        <v>-28.520109035969089</v>
       </c>
       <c r="B50">
-        <v>-26.004113407976622</v>
+        <v>-22.017682258659946</v>
       </c>
       <c r="C50">
         <v>338.08353538342624</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-30.676007616259952</v>
+        <v>-26.509008354127136</v>
       </c>
       <c r="B51">
-        <v>-23.801011102132065</v>
+        <v>-19.815858750288516</v>
       </c>
       <c r="C51">
         <v>338.08353538342624</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-28.654534365034522</v>
+        <v>-24.489611038605641</v>
       </c>
       <c r="B52">
-        <v>-21.609641627445978</v>
+        <v>-17.622364133883067</v>
       </c>
       <c r="C52">
         <v>338.08353538342624</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-26.622222596005766</v>
+        <v>-22.461834419138661</v>
       </c>
       <c r="B53">
-        <v>-19.429147782220372</v>
+        <v>-15.437281401141233</v>
       </c>
       <c r="C53">
         <v>338.08353538342624</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-24.579926585783436</v>
+        <v>-20.42559582546026</v>
       </c>
       <c r="B54">
-        <v>-17.258672364757295</v>
+        <v>-13.260693543760656</v>
       </c>
       <c r="C54">
         <v>338.08353538342624</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-22.528299095191038</v>
+        <v>-18.380804294698219</v>
       </c>
       <c r="B55">
-        <v>-15.097560379145719</v>
+        <v>-11.0926918782879</v>
       </c>
       <c r="C55">
         <v>338.08353538342624</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-20.467186821907038</v>
+        <v>-16.32733569355516</v>
       </c>
       <c r="B56">
-        <v>-12.945965652622416</v>
+        <v>-8.93340102066517</v>
       </c>
       <c r="C56">
         <v>338.08353538342624</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-18.396234947823643</v>
+        <v>-14.265057596127427</v>
       </c>
       <c r="B57">
-        <v>-10.804244218211107</v>
+        <v>-6.7829539116836033</v>
       </c>
       <c r="C57">
         <v>338.08353538342624</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-16.315088654833076</v>
+        <v>-12.193837576511369</v>
       </c>
       <c r="B58">
-        <v>-8.6727521089355157</v>
+        <v>-4.6414834921343191</v>
       </c>
       <c r="C58">
         <v>338.08353538342624</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-14.223435911098855</v>
+        <v>-10.113600209202042</v>
       </c>
       <c r="B59">
-        <v>-6.55180242504559</v>
+        <v>-2.5090654807854866</v>
       </c>
       <c r="C59">
         <v>338.08353538342624</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-12.121135829869795</v>
+        <v>-8.02449807028936</v>
       </c>
       <c r="B60">
-        <v>-4.4415365356962022</v>
+        <v>-0.38554670831342575</v>
       </c>
       <c r="C60">
         <v>338.08353538342624</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-10.008090310666015</v>
+        <v>-5.926740736261956</v>
       </c>
       <c r="B61">
-        <v>-2.3420528772684466</v>
+        <v>1.7292832166285006</v>
       </c>
       <c r="C61">
         <v>338.08353538342624</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-7.8842012530076362</v>
+        <v>-3.8205377836084518</v>
       </c>
       <c r="B62">
-        <v>-0.25344988614341929</v>
+        <v>3.835634685386935</v>
       </c>
       <c r="C62">
         <v>338.08353538342624</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.7496375471943937</v>
+        <v>-1.70602892998795</v>
       </c>
       <c r="B63">
-        <v>1.8244419062678903</v>
+        <v>5.9336479588596216</v>
       </c>
       <c r="C63">
         <v>338.08353538342624</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-3.60563604664436</v>
+        <v>0.41692554225865663</v>
       </c>
       <c r="B64">
-        <v>3.8928635884349965</v>
+        <v>8.02318277614882</v>
       </c>
       <c r="C64">
         <v>338.08353538342624</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.4537005955552502</v>
+        <v>2.548535209619978</v>
       </c>
       <c r="B65">
-        <v>5.9533241537974968</v>
+        <v>10.104028745907877</v>
       </c>
       <c r="C65">
         <v>338.08353538342624</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>0.70466496187526806</v>
+        <v>4.6890096485846611</v>
       </c>
       <c r="B66">
-        <v>8.00733259579503</v>
+        <v>12.175975476790168</v>
       </c>
       <c r="C66">
         <v>338.08353538342624</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2.8699055350977178</v>
+        <v>6.83850143524261</v>
       </c>
       <c r="B67">
-        <v>10.054442481583591</v>
+        <v>14.238869799472006</v>
       </c>
       <c r="C67">
         <v>338.08353538342624</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5.0502610481555532</v>
+        <v>8.9969351440888818</v>
       </c>
       <c r="B68">
-        <v>12.0863856731848</v>
+        <v>16.29278743272156</v>
       </c>
       <c r="C68">
         <v>338.08353538342624</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>7.2521169306100752</v>
+        <v>11.164178349219828</v>
       </c>
       <c r="B69">
-        <v>14.096754876989426</v>
+        <v>18.337861317329953</v>
       </c>
       <c r="C69">
         <v>338.08353538342624</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>9.4666456195010689</v>
+        <v>13.340098624731791</v>
       </c>
       <c r="B70">
-        <v>16.0944078819993</v>
+        <v>20.374224394088316</v>
       </c>
       <c r="C70">
         <v>338.08353538342624</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>11.684222615007636</v>
+        <v>15.524571837327398</v>
       </c>
       <c r="B71">
-        <v>18.089002142830818</v>
+        <v>22.402001278938858</v>
       </c>
       <c r="C71">
         <v>338.08353538342624</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>13.907248662387644</v>
+        <v>17.717507024134427</v>
       </c>
       <c r="B72">
-        <v>20.078128693947612</v>
+        <v>24.421283288428146</v>
       </c>
       <c r="C72">
         <v>338.08353538342624</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>16.139725439317978</v>
+        <v>19.918821514886943</v>
       </c>
       <c r="B73">
-        <v>22.057772155717156</v>
+        <v>26.432153414253818</v>
       </c>
       <c r="C73">
         <v>338.08353538342624</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>18.380033108072855</v>
+        <v>22.128432639318994</v>
       </c>
       <c r="B74">
-        <v>24.029557912275124</v>
+        <v>28.434694648113517</v>
       </c>
       <c r="C74">
         <v>338.08353538342624</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>20.625116307232844</v>
+        <v>24.345747541341407</v>
       </c>
       <c r="B75">
-        <v>25.996551786759756</v>
+        <v>30.429502151190555</v>
       </c>
       <c r="C75">
         <v>338.08353538342624</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>22.871799096006558</v>
+        <v>26.568132621572008</v>
       </c>
       <c r="B76">
-        <v>27.961940594551383</v>
+        <v>32.419219762610886</v>
       </c>
       <c r="C76">
         <v>338.08353538342624</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>25.11714382064687</v>
+        <v>28.794257143494836</v>
       </c>
       <c r="B77">
-        <v>29.928672048078653</v>
+        <v>34.405183392950384</v>
       </c>
       <c r="C77">
         <v>338.08353538342624</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>27.359286554955624</v>
+        <v>31.030042565351753</v>
       </c>
       <c r="B78">
-        <v>31.898616455721417</v>
+        <v>36.381448560641907</v>
       </c>
       <c r="C78">
         <v>338.08353538342624</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>29.595033471156896</v>
+        <v>33.281115721172391</v>
       </c>
       <c r="B79">
-        <v>33.874978581090517</v>
+        <v>38.342366553864053</v>
       </c>
       <c r="C79">
         <v>338.08353538342624</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>31.818763956660078</v>
+        <v>35.544672753379643</v>
       </c>
       <c r="B80">
-        <v>35.863398282050795</v>
+        <v>40.2907521319216</v>
       </c>
       <c r="C80">
         <v>338.08353538342624</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>34.016635548091919</v>
+        <v>37.815802131494721</v>
       </c>
       <c r="B81">
-        <v>37.877765419300921</v>
+        <v>42.231535921900843</v>
       </c>
       <c r="C81">
         <v>338.08353538342624</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>35.938888349939567</v>
+        <v>40.089592325038836</v>
       </c>
       <c r="B82">
-        <v>40.168695079421653</v>
+        <v>44.16964855088807</v>
       </c>
       <c r="C82">
         <v>338.08353538342624</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>39.075181474427993</v>
+        <v>38.16150082847723</v>
       </c>
       <c r="B1">
-        <v>45.876068453021695</v>
+        <v>46.638860604478168</v>
       </c>
       <c r="C1">
         <v>592.998505179033</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>35.645643814335259</v>
+        <v>34.575844666311362</v>
       </c>
       <c r="B2">
-        <v>44.518044179625946</v>
+        <v>45.377983442775204</v>
       </c>
       <c r="C2">
         <v>592.998505179033</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>32.78976478738501</v>
+        <v>31.688439198775807</v>
       </c>
       <c r="B3">
-        <v>42.624891183338548</v>
+        <v>43.491082859660125</v>
       </c>
       <c r="C3">
         <v>592.998505179033</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>30.02504121177364</v>
+        <v>28.909730480063242</v>
       </c>
       <c r="B4">
-        <v>40.646705211965639</v>
+        <v>41.506729153880322</v>
       </c>
       <c r="C4">
         <v>592.998505179033</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>27.324648683168647</v>
+        <v>26.2069465008103</v>
       </c>
       <c r="B5">
-        <v>38.608509002730145</v>
+        <v>39.454304387760928</v>
       </c>
       <c r="C5">
         <v>592.998505179033</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>24.67764827569216</v>
+        <v>23.566725082610233</v>
       </c>
       <c r="B6">
-        <v>36.520506766109591</v>
+        <v>37.34578855173811</v>
       </c>
       <c r="C6">
         <v>592.998505179033</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>22.077794837384182</v>
+        <v>20.981438955973658</v>
       </c>
       <c r="B7">
-        <v>34.388524197037405</v>
+        <v>35.188019948127206</v>
       </c>
       <c r="C7">
         <v>592.998505179033</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>19.52141514364606</v>
+        <v>18.446603276329288</v>
       </c>
       <c r="B8">
-        <v>32.21598780716144</v>
+        <v>32.985019507755219</v>
       </c>
       <c r="C8">
         <v>592.998505179033</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>17.002769177857729</v>
+        <v>15.955207514859412</v>
       </c>
       <c r="B9">
-        <v>30.00825208360321</v>
+        <v>30.743072588116412</v>
       </c>
       <c r="C9">
         <v>592.998505179033</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>14.515660135174459</v>
+        <v>13.499682846600736</v>
       </c>
       <c r="B10">
-        <v>27.771097621425636</v>
+        <v>28.468965092520346</v>
       </c>
       <c r="C10">
         <v>592.998505179033</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>12.054130849874431</v>
+        <v>11.072752946253962</v>
       </c>
       <c r="B11">
-        <v>25.510081471983998</v>
+        <v>26.169220680870549</v>
       </c>
       <c r="C11">
         <v>592.998505179033</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>9.615000191374806</v>
+        <v>8.67053330150306</v>
       </c>
       <c r="B12">
-        <v>23.228171104514882</v>
+        <v>23.847322050297581</v>
       </c>
       <c r="C12">
         <v>592.998505179033</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>7.2059515305257289</v>
+        <v>6.3024141523010337</v>
       </c>
       <c r="B13">
-        <v>20.918199203487745</v>
+        <v>21.494850290246148</v>
       </c>
       <c r="C13">
         <v>592.998505179033</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>4.8315794539419281</v>
+        <v>3.9740114752465812</v>
       </c>
       <c r="B14">
-        <v>18.57587977872431</v>
+        <v>19.106770342517379</v>
       </c>
       <c r="C14">
         <v>592.998505179033</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>2.4732589098633806</v>
+        <v>1.6625694412520184</v>
       </c>
       <c r="B15">
-        <v>16.21858692622224</v>
+        <v>16.703484166023824</v>
       </c>
       <c r="C15">
         <v>592.998505179033</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>0.11390709514012917</v>
+        <v>-0.65278348221964577</v>
       </c>
       <c r="B16">
-        <v>13.862256078841659</v>
+        <v>14.303704335360013</v>
       </c>
       <c r="C16">
         <v>592.998505179033</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.234170160562936</v>
+        <v>-2.9570098358164629</v>
       </c>
       <c r="B17">
-        <v>11.495407930716215</v>
+        <v>11.893948870736647</v>
       </c>
       <c r="C17">
         <v>592.998505179033</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.5550811831991878</v>
+        <v>-5.2306908900407665</v>
       </c>
       <c r="B18">
-        <v>9.10321817563684</v>
+        <v>9.4568077221915914</v>
       </c>
       <c r="C18">
         <v>592.998505179033</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-6.8479795540099815</v>
+        <v>-7.4727918267009974</v>
       </c>
       <c r="B19">
-        <v>6.6848972447499326</v>
+        <v>6.9913531134551175</v>
       </c>
       <c r="C19">
         <v>592.998505179033</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-9.1157801680587</v>
+        <v>-9.6868738054321675</v>
       </c>
       <c r="B20">
-        <v>4.2431642535407148</v>
+        <v>4.5007778366805677</v>
       </c>
       <c r="C20">
         <v>592.998505179033</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-11.361397920408692</v>
+        <v>-11.87649798586925</v>
       </c>
       <c r="B21">
-        <v>1.7807383174944522</v>
+        <v>1.988274684021317</v>
       </c>
       <c r="C21">
         <v>592.998505179033</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-13.587228669860854</v>
+        <v>-14.044591486169834</v>
       </c>
       <c r="B22">
-        <v>-0.7001456229795916</v>
+        <v>-0.54353200839528559</v>
       </c>
       <c r="C22">
         <v>592.998505179033</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-15.793592130166116</v>
+        <v>-16.19154525858178</v>
       </c>
       <c r="B23">
-        <v>-3.1991893277759549</v>
+        <v>-3.0942917285458025</v>
       </c>
       <c r="C23">
         <v>592.998505179033</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-17.980288978812972</v>
+        <v>-18.317116213875568</v>
       </c>
       <c r="B24">
-        <v>-5.716578731865174</v>
+        <v>-5.6642224204328224</v>
       </c>
       <c r="C24">
         <v>592.998505179033</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-20.147119893289876</v>
+        <v>-20.421061262821652</v>
       </c>
       <c r="B25">
-        <v>-8.2524997702177547</v>
+        <v>-8.2535420280589022</v>
       </c>
       <c r="C25">
         <v>592.998505179033</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-22.293799679456562</v>
+        <v>-22.503032541873885</v>
       </c>
       <c r="B26">
-        <v>-10.807218481845794</v>
+        <v>-10.862562431854673</v>
       </c>
       <c r="C26">
         <v>592.998505179033</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-24.419699656657947</v>
+        <v>-24.562263090219773</v>
       </c>
       <c r="B27">
-        <v>-13.381321321927757</v>
+        <v>-13.491971257963057</v>
       </c>
       <c r="C27">
         <v>592.998505179033</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-26.524105272610218</v>
+        <v>-26.597881172730215</v>
       </c>
       <c r="B28">
-        <v>-15.975474849683701</v>
+        <v>-16.14255006895506</v>
       </c>
       <c r="C28">
         <v>592.998505179033</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-28.606301975029535</v>
+        <v>-28.609015054276092</v>
       </c>
       <c r="B29">
-        <v>-18.590345624333668</v>
+        <v>-18.815080427401647</v>
       </c>
       <c r="C29">
         <v>592.998505179033</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-30.665961151759333</v>
+        <v>-30.595264721998724</v>
       </c>
       <c r="B30">
-        <v>-21.226240186725295</v>
+        <v>-21.50992096870457</v>
       </c>
       <c r="C30">
         <v>592.998505179033</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-32.704297951152128</v>
+        <v>-32.558117052121183</v>
       </c>
       <c r="B31">
-        <v>-23.882025004216647</v>
+        <v>-24.225738619588675</v>
       </c>
       <c r="C31">
         <v>592.998505179033</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-34.722913461687696</v>
+        <v>-34.499530643136971</v>
       </c>
       <c r="B32">
-        <v>-26.5562065257934</v>
+        <v>-26.960777379609578</v>
       </c>
       <c r="C32">
         <v>592.998505179033</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-36.723408771845783</v>
+        <v>-36.421464093539548</v>
       </c>
       <c r="B33">
-        <v>-29.2472912004412</v>
+        <v>-29.713281248322872</v>
       </c>
       <c r="C33">
         <v>592.998505179033</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-38.706760221189221</v>
+        <v>-38.325112796298939</v>
       </c>
       <c r="B34">
-        <v>-31.954368264662094</v>
+        <v>-32.482178484586356</v>
       </c>
       <c r="C34">
         <v>592.998505179033</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-40.671445153613035</v>
+        <v>-40.208619322291142</v>
       </c>
       <c r="B35">
-        <v>-34.678858105023586</v>
+        <v>-35.2691343844666</v>
       </c>
       <c r="C35">
         <v>592.998505179033</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-42.615316164095276</v>
+        <v>-42.06936303686863</v>
       </c>
       <c r="B36">
-        <v>-37.422763895609563</v>
+        <v>-38.0764985033323</v>
       </c>
       <c r="C36">
         <v>592.998505179033</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-44.536225847614084</v>
+        <v>-43.904723305383968</v>
       </c>
       <c r="B37">
-        <v>-40.188088810503935</v>
+        <v>-40.906620396552235</v>
       </c>
       <c r="C37">
         <v>592.998505179033</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-46.430495336809138</v>
+        <v>-45.710208383032061</v>
       </c>
       <c r="B38">
-        <v>-42.978264625118861</v>
+        <v>-43.763527181424806</v>
       </c>
       <c r="C38">
         <v>592.998505179033</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-48.288319914966635</v>
+        <v>-47.473842084377587</v>
       </c>
       <c r="B39">
-        <v>-45.802437520179694</v>
+        <v>-46.657956222967115</v>
       </c>
       <c r="C39">
         <v>592.998505179033</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-50.098363403034412</v>
+        <v>-49.181777113827607</v>
       </c>
       <c r="B40">
-        <v>-48.671182277740023</v>
+        <v>-49.602322448125967</v>
       </c>
       <c r="C40">
         <v>592.998505179033</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-51.849289621960267</v>
+        <v>-50.82016617578924</v>
       </c>
       <c r="B41">
-        <v>-51.595073679853485</v>
+        <v>-52.609040783848094</v>
       </c>
       <c r="C41">
         <v>592.998505179033</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-51.849289621960267</v>
+        <v>-50.82016617578924</v>
       </c>
       <c r="B42">
-        <v>-51.595073679853485</v>
+        <v>-52.609040783848094</v>
       </c>
       <c r="C42">
         <v>592.998505179033</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-49.563627274777367</v>
+        <v>-48.528396791840436</v>
       </c>
       <c r="B43">
-        <v>-49.170002734482196</v>
+        <v>-50.188116902466355</v>
       </c>
       <c r="C43">
         <v>592.998505179033</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-47.310684359373894</v>
+        <v>-46.279294343267694</v>
       </c>
       <c r="B44">
-        <v>-46.71440996527646</v>
+        <v>-47.728939567030466</v>
       </c>
       <c r="C44">
         <v>592.998505179033</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-45.079164864795047</v>
+        <v>-44.059052434782309</v>
       </c>
       <c r="B45">
-        <v>-44.238832684091804</v>
+        <v>-45.243887034923468</v>
       </c>
       <c r="C45">
         <v>592.998505179033</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-42.857772780085973</v>
+        <v>-41.853864671095593</v>
       </c>
       <c r="B46">
-        <v>-41.753808202783738</v>
+        <v>-42.745337563528395</v>
       </c>
       <c r="C46">
         <v>592.998505179033</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-40.636742139607605</v>
+        <v>-39.651794324223481</v>
       </c>
       <c r="B47">
-        <v>-39.268446553727479</v>
+        <v>-40.24399314190233</v>
       </c>
       <c r="C47">
         <v>592.998505179033</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-38.412427158983867</v>
+        <v>-37.448383335400528</v>
       </c>
       <c r="B48">
-        <v>-36.786148651377026</v>
+        <v>-37.743850685798712</v>
       </c>
       <c r="C48">
         <v>592.998505179033</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-36.182712099154386</v>
+        <v>-35.241043313165889</v>
       </c>
       <c r="B49">
-        <v>-34.308888130706052</v>
+        <v>-35.247230842645024</v>
       </c>
       <c r="C49">
         <v>592.998505179033</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-33.945481221058834</v>
+        <v>-33.027185866058787</v>
       </c>
       <c r="B50">
-        <v>-31.838638626688265</v>
+        <v>-32.756454259868782</v>
       </c>
       <c r="C50">
         <v>592.998505179033</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-31.699241971938992</v>
+        <v>-30.804984217042826</v>
       </c>
       <c r="B51">
-        <v>-29.376792444442472</v>
+        <v>-30.273158752110614</v>
       </c>
       <c r="C51">
         <v>592.998505179033</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-29.444994544244913</v>
+        <v>-28.575658046779214</v>
       </c>
       <c r="B52">
-        <v>-26.922416569667909</v>
+        <v>-27.79625080286354</v>
       </c>
       <c r="C52">
         <v>592.998505179033</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-27.184362316728812</v>
+        <v>-26.341188650353605</v>
       </c>
       <c r="B53">
-        <v>-24.473996658208982</v>
+        <v>-25.323954062833732</v>
       </c>
       <c r="C53">
         <v>592.998505179033</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-24.918968668142867</v>
+        <v>-24.103557322851632</v>
       </c>
       <c r="B54">
-        <v>-22.030018365910038</v>
+        <v>-22.854492182727327</v>
       </c>
       <c r="C54">
         <v>592.998505179033</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-22.65004954476429</v>
+        <v>-21.864272117537443</v>
       </c>
       <c r="B55">
-        <v>-19.589328759101658</v>
+        <v>-20.386513102787898</v>
       </c>
       <c r="C55">
         <v>592.998505179033</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-20.377291162970547</v>
+        <v>-19.6229481203893</v>
       </c>
       <c r="B56">
-        <v>-17.152220546059304</v>
+        <v>-17.920361921408759</v>
       </c>
       <c r="C56">
         <v>592.998505179033</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-18.099992306664138</v>
+        <v>-17.378727175564002</v>
       </c>
       <c r="B57">
-        <v>-14.719347845544641</v>
+        <v>-15.456808026520656</v>
       </c>
       <c r="C57">
         <v>592.998505179033</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-15.817451759747559</v>
+        <v>-15.130751127218309</v>
       </c>
       <c r="B58">
-        <v>-12.29136477631932</v>
+        <v>-12.99662080605432</v>
       </c>
       <c r="C58">
         <v>592.998505179033</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-13.529052704428983</v>
+        <v>-12.878265093646</v>
       </c>
       <c r="B59">
-        <v>-9.8688467274703626</v>
+        <v>-10.540477056512948</v>
       </c>
       <c r="C59">
         <v>592.998505179033</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-11.234515916139369</v>
+        <v>-10.620927289688877</v>
       </c>
       <c r="B60">
-        <v>-7.4520541693862654</v>
+        <v>-8.08868320868963</v>
       </c>
       <c r="C60">
         <v>592.998505179033</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-8.933646568615373</v>
+        <v>-8.3584992043257458</v>
       </c>
       <c r="B61">
-        <v>-5.0411688427808956</v>
+        <v>-5.6414531019499377</v>
       </c>
       <c r="C61">
         <v>592.998505179033</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-6.6262498355936161</v>
+        <v>-6.0907423265353842</v>
       </c>
       <c r="B62">
-        <v>-2.6363724883680888</v>
+        <v>-3.1990005756594004</v>
       </c>
       <c r="C62">
         <v>592.998505179033</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-4.3126483991022742</v>
+        <v>-3.8180506309503475</v>
       </c>
       <c r="B63">
-        <v>-0.23736409713021175</v>
+        <v>-0.76097240804639854</v>
       </c>
       <c r="C63">
         <v>592.998505179033</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.9952349743355746</v>
+        <v>-1.5433480348180984</v>
       </c>
       <c r="B64">
-        <v>2.1580883388764396</v>
+        <v>1.6752528672095282</v>
       </c>
       <c r="C64">
         <v>592.998505179033</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>0.32308021522070529</v>
+        <v>0.72980905896012249</v>
       </c>
       <c r="B65">
-        <v>4.55269957732704</v>
+        <v>4.1128637775659946</v>
       </c>
       <c r="C65">
         <v>592.998505179033</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>2.6393869460808239</v>
+        <v>2.997864247483113</v>
       </c>
       <c r="B66">
-        <v>6.9491843758968015</v>
+        <v>6.5550488504806568</v>
       </c>
       <c r="C66">
         <v>592.998505179033</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>4.9545375382305821</v>
+        <v>5.2618583577404978</v>
       </c>
       <c r="B67">
-        <v>9.34674766086215</v>
+        <v>9.0008749224376423</v>
       </c>
       <c r="C67">
         <v>592.998505179033</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>7.2844344855421008</v>
+        <v>7.54122113628536</v>
       </c>
       <c r="B68">
-        <v>11.730555032904515</v>
+        <v>11.432922066027111</v>
       </c>
       <c r="C68">
         <v>592.998505179033</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>9.6413962139075</v>
+        <v>9.8510028683080488</v>
       </c>
       <c r="B69">
-        <v>14.0891154359588</v>
+        <v>13.837696802330205</v>
       </c>
       <c r="C69">
         <v>592.998505179033</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>12.008354703412488</v>
+        <v>12.170347073984434</v>
       </c>
       <c r="B70">
-        <v>16.438350512568697</v>
+        <v>16.2338982102859</v>
       </c>
       <c r="C70">
         <v>592.998505179033</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>14.366701034543553</v>
+        <v>14.476514350541098</v>
       </c>
       <c r="B71">
-        <v>18.795619310011389</v>
+        <v>18.641913521635725</v>
       </c>
       <c r="C71">
         <v>592.998505179033</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>16.721049135196495</v>
+        <v>16.775140368421635</v>
       </c>
       <c r="B72">
-        <v>21.156617795888927</v>
+        <v>21.056690021473415</v>
       </c>
       <c r="C72">
         <v>592.998505179033</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>19.079103262724832</v>
+        <v>19.075636634813453</v>
       </c>
       <c r="B73">
-        <v>23.514159171014086</v>
+        <v>23.46978973189875</v>
       </c>
       <c r="C73">
         <v>592.998505179033</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>21.437706144903551</v>
+        <v>21.374142930662028</v>
       </c>
       <c r="B74">
-        <v>25.871188648717546</v>
+        <v>25.884673569683461</v>
       </c>
       <c r="C74">
         <v>592.998505179033</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>23.790925976535288</v>
+        <v>23.663408753478542</v>
       </c>
       <c r="B75">
-        <v>28.233239623175415</v>
+        <v>28.307842043040292</v>
       </c>
       <c r="C75">
         <v>592.998505179033</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>26.132594350111784</v>
+        <v>25.935894193278905</v>
       </c>
       <c r="B76">
-        <v>30.606066199427648</v>
+        <v>30.746055131274215</v>
       </c>
       <c r="C76">
         <v>592.998505179033</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>28.457001201621726</v>
+        <v>28.184619219847328</v>
       </c>
       <c r="B77">
-        <v>32.9949949237606</v>
+        <v>33.205570848062642</v>
       </c>
       <c r="C77">
         <v>592.998505179033</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>30.760506443352497</v>
+        <v>30.4051327295365</v>
       </c>
       <c r="B78">
-        <v>35.403421396582459</v>
+        <v>35.69037987348046</v>
       </c>
       <c r="C78">
         <v>592.998505179033</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>33.036899503679479</v>
+        <v>32.589842663542377</v>
       </c>
       <c r="B79">
-        <v>37.837139055087249</v>
+        <v>38.207288941362123</v>
       </c>
       <c r="C79">
         <v>592.998505179033</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>35.275278911773327</v>
+        <v>34.725424981258591</v>
       </c>
       <c r="B80">
-        <v>40.306317170380652</v>
+        <v>40.768243849329572</v>
       </c>
       <c r="C80">
         <v>592.998505179033</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>37.448859943793444</v>
+        <v>36.779148077132206</v>
       </c>
       <c r="B81">
-        <v>42.835941464342767</v>
+        <v>43.402590435280487</v>
       </c>
       <c r="C81">
         <v>592.998505179033</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>39.075181474427993</v>
+        <v>38.16150082847723</v>
       </c>
       <c r="B82">
-        <v>45.876068453021695</v>
+        <v>46.638860604478168</v>
       </c>
       <c r="C82">
         <v>592.998505179033</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>40.593055650623654</v>
+        <v>39.183734434796442</v>
       </c>
       <c r="B1">
-        <v>50.287725686991507</v>
+        <v>51.393447807751556</v>
       </c>
       <c r="C1">
         <v>767.45943045334911</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>36.590262542981328</v>
+        <v>34.809699265245804</v>
       </c>
       <c r="B2">
-        <v>49.043767187850875</v>
+        <v>50.376676247712886</v>
       </c>
       <c r="C2">
         <v>767.45943045334911</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>33.46595494105496</v>
+        <v>31.58832296518003</v>
       </c>
       <c r="B3">
-        <v>47.0294106520228</v>
+        <v>48.404261333469449</v>
       </c>
       <c r="C3">
         <v>767.45943045334911</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>30.4751562496387</v>
+        <v>28.538871378656598</v>
       </c>
       <c r="B4">
-        <v>44.897971931152348</v>
+        <v>46.289307534331364</v>
       </c>
       <c r="C4">
         <v>767.45943045334911</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>27.576463707068356</v>
+        <v>25.6068437387951</v>
       </c>
       <c r="B5">
-        <v>42.68575965650551</v>
+        <v>44.077000201357109</v>
       </c>
       <c r="C5">
         <v>767.45943045334911</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>24.753001142848902</v>
+        <v>22.770027531455515</v>
       </c>
       <c r="B6">
-        <v>40.40757358121602</v>
+        <v>41.785755226776409</v>
       </c>
       <c r="C6">
         <v>767.45943045334911</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>21.995138584198688</v>
+        <v>20.015749302858293</v>
       </c>
       <c r="B7">
-        <v>38.0718588214253</v>
+        <v>39.426079883989821</v>
       </c>
       <c r="C7">
         <v>767.45943045334911</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>19.297216621352106</v>
+        <v>17.336562554527944</v>
       </c>
       <c r="B8">
-        <v>35.683578462060616</v>
+        <v>37.0041478961765</v>
       </c>
       <c r="C8">
         <v>767.45943045334911</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>16.650383518091203</v>
+        <v>14.720817809684128</v>
       </c>
       <c r="B9">
-        <v>33.250495135697271</v>
+        <v>34.529617580606029</v>
       </c>
       <c r="C9">
         <v>767.45943045334911</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>14.045081680058445</v>
+        <v>12.155936166277179</v>
       </c>
       <c r="B10">
-        <v>30.780990485379533</v>
+        <v>32.01291781998188</v>
       </c>
       <c r="C10">
         <v>767.45943045334911</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>11.472122406790456</v>
+        <v>9.6298239994849286</v>
       </c>
       <c r="B11">
-        <v>28.28312264837961</v>
+        <v>29.464075164652563</v>
       </c>
       <c r="C11">
         <v>767.45943045334911</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>8.9266026869588817</v>
+        <v>7.13602948617182</v>
       </c>
       <c r="B12">
-        <v>25.76119137725648</v>
+        <v>26.888438675008118</v>
       </c>
       <c r="C12">
         <v>767.45943045334911</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>6.4203933718814072</v>
+        <v>4.6901827327213361</v>
       </c>
       <c r="B13">
-        <v>23.204786391488188</v>
+        <v>24.273049783959596</v>
       </c>
       <c r="C13">
         <v>767.45943045334911</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>3.9605956202023798</v>
+        <v>2.3016345055624741</v>
       </c>
       <c r="B14">
-        <v>20.60768024777353</v>
+        <v>21.610155982910452</v>
       </c>
       <c r="C14">
         <v>767.45943045334911</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>1.518457957226665</v>
+        <v>-0.0674637182127829</v>
       </c>
       <c r="B15">
-        <v>17.995086884774945</v>
+        <v>18.931136624712622</v>
       </c>
       <c r="C15">
         <v>767.45943045334911</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.93239032960385892</v>
+        <v>-2.4518264208224081</v>
       </c>
       <c r="B16">
-        <v>15.390132404230789</v>
+        <v>16.264772700086397</v>
       </c>
       <c r="C16">
         <v>767.45943045334911</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.3729442709600312</v>
+        <v>-4.826432632387367</v>
       </c>
       <c r="B17">
-        <v>12.7761501782192</v>
+        <v>13.590319889776778</v>
       </c>
       <c r="C17">
         <v>767.45943045334911</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-5.778662948629961</v>
+        <v>-7.1589736855896433</v>
       </c>
       <c r="B18">
-        <v>10.131618764341949</v>
+        <v>10.880991809691253</v>
       </c>
       <c r="C18">
         <v>767.45943045334911</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-8.1482373307581675</v>
+        <v>-9.4477255754523615</v>
       </c>
       <c r="B19">
-        <v>7.4553901919554262</v>
+        <v>8.1353591263623457</v>
       </c>
       <c r="C19">
         <v>767.45943045334911</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-10.486166357078323</v>
+        <v>-11.698610462583964</v>
       </c>
       <c r="B20">
-        <v>4.751409858354652</v>
+        <v>5.35833176897881</v>
       </c>
       <c r="C20">
         <v>767.45943045334911</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-12.79694896732406</v>
+        <v>-13.917550507592871</v>
       </c>
       <c r="B21">
-        <v>2.0236231608346622</v>
+        <v>2.5548196667294163</v>
       </c>
       <c r="C21">
         <v>767.45943045334911</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-15.084283257964607</v>
+        <v>-16.109413767492857</v>
       </c>
       <c r="B22">
-        <v>-0.72472681208363576</v>
+        <v>-0.27114118460576286</v>
       </c>
       <c r="C22">
         <v>767.45943045334911</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-17.348663952411478</v>
+        <v>-18.27485188491907</v>
       </c>
       <c r="B23">
-        <v>-3.4932062069758492</v>
+        <v>-3.1190105228814553</v>
       </c>
       <c r="C23">
         <v>767.45943045334911</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-19.589784930811767</v>
+        <v>-20.413462398912014</v>
       </c>
       <c r="B24">
-        <v>-6.2820834791917246</v>
+        <v>-5.9891220193610915</v>
       </c>
       <c r="C24">
         <v>767.45943045334911</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-21.807340073312545</v>
+        <v>-22.524842848512172</v>
       </c>
       <c r="B25">
-        <v>-9.0916270840809759</v>
+        <v>-8.8818093453080778</v>
       </c>
       <c r="C25">
         <v>767.45943045334911</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-24.000891209802941</v>
+        <v>-24.608417108300831</v>
       </c>
       <c r="B26">
-        <v>-11.922221279996135</v>
+        <v>-11.797550153254441</v>
       </c>
       <c r="C26">
         <v>767.45943045334911</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-26.169471969140254</v>
+        <v>-26.662914395022476</v>
       </c>
       <c r="B27">
-        <v>-14.77471353730096</v>
+        <v>-14.737398020806667</v>
       </c>
       <c r="C27">
         <v>767.45943045334911</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-28.3119839299238</v>
+        <v>-28.686890260962365</v>
       </c>
       <c r="B28">
-        <v>-17.650067129361968</v>
+        <v>-17.702550506839827</v>
       </c>
       <c r="C28">
         <v>767.45943045334911</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-30.4273286707529</v>
+        <v>-30.678900258405768</v>
       </c>
       <c r="B29">
-        <v>-20.549245329545691</v>
+        <v>-20.694205170229</v>
       </c>
       <c r="C29">
         <v>767.45943045334911</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-32.515004212244108</v>
+        <v>-32.6382853151761</v>
       </c>
       <c r="B30">
-        <v>-23.472688354485108</v>
+        <v>-23.712908432783912</v>
       </c>
       <c r="C30">
         <v>767.45943045334911</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-34.576894343082984</v>
+        <v>-34.567527861249438</v>
       </c>
       <c r="B31">
-        <v>-26.418744193879025</v>
+        <v>-26.756602168052979</v>
       </c>
       <c r="C31">
         <v>767.45943045334911</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-36.615479293972335</v>
+        <v>-36.469895702140072</v>
       </c>
       <c r="B32">
-        <v>-29.385237780692741</v>
+        <v>-29.822577112519326</v>
       </c>
       <c r="C32">
         <v>767.45943045334911</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-38.633239295614942</v>
+        <v>-38.348656643362233</v>
       </c>
       <c r="B33">
-        <v>-32.369994047891517</v>
+        <v>-32.90812400266605</v>
       </c>
       <c r="C33">
         <v>767.45943045334911</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-40.631690529789651</v>
+        <v>-40.205809534598394</v>
       </c>
       <c r="B34">
-        <v>-35.371683362307763</v>
+        <v>-36.011585637507089</v>
       </c>
       <c r="C34">
         <v>767.45943045334911</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-42.608492982579335</v>
+        <v>-42.038277402203832</v>
       </c>
       <c r="B35">
-        <v>-38.392357826242311</v>
+        <v>-39.135513066179762</v>
       </c>
       <c r="C35">
         <v>767.45943045334911</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-44.560342591142891</v>
+        <v>-43.841714316702053</v>
       </c>
       <c r="B36">
-        <v>-41.434914975863158</v>
+        <v>-42.283509400352209</v>
       </c>
       <c r="C36">
         <v>767.45943045334911</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-46.483935292639295</v>
+        <v>-45.611774348616557</v>
       </c>
       <c r="B37">
-        <v>-44.502252347338313</v>
+        <v>-45.459177751692643</v>
       </c>
       <c r="C37">
         <v>767.45943045334911</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-48.373602945375559</v>
+        <v>-47.340999497661443</v>
       </c>
       <c r="B38">
-        <v>-47.599340683159788</v>
+        <v>-48.668701379270637</v>
       </c>
       <c r="C38">
         <v>767.45943045334911</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-50.214221092251364</v>
+        <v>-49.009483480313072</v>
       </c>
       <c r="B39">
-        <v>-50.739443551115848</v>
+        <v>-51.928584131761539</v>
       </c>
       <c r="C39">
         <v>767.45943045334911</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-51.988301197314534</v>
+        <v>-50.594207942238413</v>
       </c>
       <c r="B40">
-        <v>-53.937897725318805</v>
+        <v>-55.2579100052421</v>
       </c>
       <c r="C40">
         <v>767.45943045334911</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-53.678354724612888</v>
+        <v>-52.072154529104445</v>
       </c>
       <c r="B41">
-        <v>-57.210039979880946</v>
+        <v>-58.675762995789107</v>
       </c>
       <c r="C41">
         <v>767.45943045334911</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-53.678354724612888</v>
+        <v>-52.072154529104445</v>
       </c>
       <c r="B42">
-        <v>-57.210039979880946</v>
+        <v>-58.675762995789107</v>
       </c>
       <c r="C42">
         <v>767.45943045334911</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-51.162660778503472</v>
+        <v>-49.507277306078613</v>
       </c>
       <c r="B43">
-        <v>-54.661952651123705</v>
+        <v>-56.159059570327116</v>
       </c>
       <c r="C43">
         <v>767.45943045334911</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-48.704737466757145</v>
+        <v>-47.022293948465958</v>
       </c>
       <c r="B44">
-        <v>-52.063202695604915</v>
+        <v>-53.576117951115805</v>
       </c>
       <c r="C44">
         <v>767.45943045334911</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-46.287128892271049</v>
+        <v>-44.594219521533923</v>
       </c>
       <c r="B45">
-        <v>-49.429098264420034</v>
+        <v>-50.945994426798293</v>
       </c>
       <c r="C45">
         <v>767.45943045334911</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-43.892379157942329</v>
+        <v>-42.200069090550016</v>
       </c>
       <c r="B46">
-        <v>-46.774947508664511</v>
+        <v>-48.28774528601771</v>
       </c>
       <c r="C46">
         <v>767.45943045334911</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-41.505395300501888</v>
+        <v>-39.8199686191832</v>
       </c>
       <c r="B47">
-        <v>-44.113986377246583</v>
+        <v>-45.617847642032594</v>
       </c>
       <c r="C47">
         <v>767.45943045334911</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-39.120536092015875</v>
+        <v>-37.446487664708421</v>
       </c>
       <c r="B48">
-        <v>-41.45116201032566</v>
+        <v>-42.94246190656321</v>
       </c>
       <c r="C48">
         <v>767.45943045334911</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-36.734523238384185</v>
+        <v>-35.075306682802079</v>
       </c>
       <c r="B49">
-        <v>-38.7893493458739</v>
+        <v>-40.265169315945172</v>
       </c>
       <c r="C49">
         <v>767.45943045334911</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-34.344078445506739</v>
+        <v>-32.702106129140596</v>
       </c>
       <c r="B50">
-        <v>-36.131423321863458</v>
+        <v>-37.589551106514172</v>
       </c>
       <c r="C50">
         <v>767.45943045334911</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-31.946886200626675</v>
+        <v>-30.323834117329746</v>
       </c>
       <c r="B51">
-        <v>-33.479414554019044</v>
+        <v>-34.918137528136533</v>
       </c>
       <c r="C51">
         <v>767.45943045334911</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-29.544482116360033</v>
+        <v>-27.942509392692635</v>
       </c>
       <c r="B52">
-        <v>-30.831976369075356</v>
+        <v>-32.24925488480131</v>
       </c>
       <c r="C52">
         <v>767.45943045334911</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-27.139364586666066</v>
+        <v>-25.561418358481731</v>
       </c>
       <c r="B53">
-        <v>-28.1869177715196</v>
+        <v>-29.580178494028196</v>
       </c>
       <c r="C53">
         <v>767.45943045334911</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-24.734032005504</v>
+        <v>-23.183847417949469</v>
       </c>
       <c r="B54">
-        <v>-25.542047765838969</v>
+        <v>-26.908183673336868</v>
       </c>
       <c r="C54">
         <v>767.45943045334911</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-22.33038511021843</v>
+        <v>-20.812296355158438</v>
       </c>
       <c r="B55">
-        <v>-22.895699478409483</v>
+        <v>-24.231197908395814</v>
       </c>
       <c r="C55">
         <v>767.45943045334911</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-19.927934011695257</v>
+        <v>-18.446118477411751</v>
       </c>
       <c r="B56">
-        <v>-20.248302523162454</v>
+        <v>-21.549757357468671</v>
       </c>
       <c r="C56">
         <v>767.45943045334911</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-17.525591164205728</v>
+        <v>-16.083880472822617</v>
       </c>
       <c r="B57">
-        <v>-17.600810635917984</v>
+        <v>-18.865050346967845</v>
       </c>
       <c r="C57">
         <v>767.45943045334911</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-15.122269022021083</v>
+        <v>-13.724149029504275</v>
       </c>
       <c r="B58">
-        <v>-14.954177552496187</v>
+        <v>-16.178265203305738</v>
       </c>
       <c r="C58">
         <v>767.45943045334911</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-12.717010888428671</v>
+        <v>-11.36566327005251</v>
       </c>
       <c r="B59">
-        <v>-12.309242259157278</v>
+        <v>-13.490447291371879</v>
       </c>
       <c r="C59">
         <v>767.45943045334911</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-10.309383462780428</v>
+        <v>-9.0078520549934229</v>
       </c>
       <c r="B60">
-        <v>-9.6663847439220074</v>
+        <v>-10.80207012996442</v>
       </c>
       <c r="C60">
         <v>767.45943045334911</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-7.899084293444429</v>
+        <v>-6.6503166793357167</v>
       </c>
       <c r="B61">
-        <v>-7.02587024525127</v>
+        <v>-8.1134642763586768</v>
       </c>
       <c r="C61">
         <v>767.45943045334911</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-5.4858109287887293</v>
+        <v>-4.2926584380880612</v>
       </c>
       <c r="B62">
-        <v>-4.3879640016059254</v>
+        <v>-5.4249602878299319</v>
       </c>
       <c r="C62">
         <v>767.45943045334911</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.0700605138993469</v>
+        <v>-1.9355314534887833</v>
       </c>
       <c r="B63">
-        <v>-1.7522300358460929</v>
+        <v>-2.7360158464500994</v>
       </c>
       <c r="C63">
         <v>767.45943045334911</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.65552858073408571</v>
+        <v>0.41619884330522622</v>
       </c>
       <c r="B64">
-        <v>0.88457249157115569</v>
+        <v>-0.042597133477554269</v>
       </c>
       <c r="C64">
         <v>767.45943045334911</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1.753289742031291</v>
+        <v>2.756614193907426</v>
       </c>
       <c r="B65">
-        <v>3.5263856357895009</v>
+        <v>2.6602025450327038</v>
       </c>
       <c r="C65">
         <v>767.45943045334911</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>4.1518993257210406</v>
+        <v>5.0797963399312938</v>
       </c>
       <c r="B66">
-        <v>6.1771514519526418</v>
+        <v>5.3772898830256981</v>
       </c>
       <c r="C66">
         <v>767.45943045334911</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6.5416140159968466</v>
+        <v>7.387474215310573</v>
       </c>
       <c r="B67">
-        <v>8.835717747893824</v>
+        <v>8.1072314605474283</v>
       </c>
       <c r="C67">
         <v>767.45943045334911</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>8.94698355587022</v>
+        <v>9.7119655232602</v>
       </c>
       <c r="B68">
-        <v>11.480555342204596</v>
+        <v>10.823233402047956</v>
       </c>
       <c r="C68">
         <v>767.45943045334911</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>11.387023187470819</v>
+        <v>12.078301752194504</v>
       </c>
       <c r="B69">
-        <v>14.094988598111812</v>
+        <v>13.504542667593034</v>
       </c>
       <c r="C69">
         <v>767.45943045334911</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>13.835374252050935</v>
+        <v>14.451780762044143</v>
       </c>
       <c r="B70">
-        <v>16.702133046625121</v>
+        <v>16.179930015307079</v>
       </c>
       <c r="C70">
         <v>767.45943045334911</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>16.263298426979894</v>
+        <v>16.794567496574992</v>
       </c>
       <c r="B71">
-        <v>19.327191092551832</v>
+        <v>18.88076363312787</v>
       </c>
       <c r="C71">
         <v>767.45943045334911</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>18.677912634972248</v>
+        <v>19.116028863377277</v>
       </c>
       <c r="B72">
-        <v>21.963921468106754</v>
+        <v>21.599277630187732</v>
       </c>
       <c r="C72">
         <v>767.45943045334911</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>21.09110474816892</v>
+        <v>21.4318123968114</v>
       </c>
       <c r="B73">
-        <v>24.601898966159947</v>
+        <v>24.322498990256893</v>
       </c>
       <c r="C73">
         <v>767.45943045334911</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>23.497991191070977</v>
+        <v>23.735486174494106</v>
       </c>
       <c r="B74">
-        <v>27.2454062947947</v>
+        <v>27.05576027446255</v>
       </c>
       <c r="C74">
         <v>767.45943045334911</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>25.889403918804735</v>
+        <v>26.014977721293576</v>
       </c>
       <c r="B75">
-        <v>29.902483477124655</v>
+        <v>29.809070498424109</v>
       </c>
       <c r="C75">
         <v>767.45943045334911</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>28.25580845663734</v>
+        <v>28.257731807827422</v>
       </c>
       <c r="B76">
-        <v>32.58149188117153</v>
+        <v>32.592838918372919</v>
       </c>
       <c r="C76">
         <v>767.45943045334911</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>30.588377448486145</v>
+        <v>30.452123920645818</v>
       </c>
       <c r="B77">
-        <v>35.290172759068639</v>
+        <v>35.4167031550468</v>
       </c>
       <c r="C77">
         <v>767.45943045334911</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>32.881478442728515</v>
+        <v>32.590735164279749</v>
       </c>
       <c r="B78">
-        <v>38.033465554487591</v>
+        <v>38.286814046597605</v>
       </c>
       <c r="C78">
         <v>767.45943045334911</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>35.125509592387608</v>
+        <v>34.660920883549537</v>
       </c>
       <c r="B79">
-        <v>40.819790718319624</v>
+        <v>41.2136549901592</v>
       </c>
       <c r="C79">
         <v>767.45943045334911</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>37.303625175362306</v>
+        <v>36.640499741062541</v>
       </c>
       <c r="B80">
-        <v>43.66392130162685</v>
+        <v>44.2156160300264</v>
       </c>
       <c r="C80">
         <v>767.45943045334911</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>39.374454673753327</v>
+        <v>38.4750039850037</v>
       </c>
       <c r="B81">
-        <v>46.602137659132254</v>
+        <v>47.337855145214988</v>
       </c>
       <c r="C81">
         <v>767.45943045334911</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>40.593055650623654</v>
+        <v>39.183734434796442</v>
       </c>
       <c r="B82">
-        <v>50.287725686991507</v>
+        <v>51.393447807751556</v>
       </c>
       <c r="C82">
         <v>767.45943045334911</v>
